--- a/scattering_plane_angles_Y2SiO5_example2.xlsx
+++ b/scattering_plane_angles_Y2SiO5_example2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\wombat_instrument_work\scattering_plane_software\siobhan_scattering_plane\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA30C00-C5AA-4146-B96E-17AB2CCB073A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C06A7BF-EDA4-4E0E-A8FD-81A9FF014B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D384836F-CCEB-43D8-9424-413C5137BC31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D384836F-CCEB-43D8-9424-413C5137BC31}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -760,8 +760,8 @@
         <v>27.456</v>
       </c>
       <c r="H10">
-        <f>+G10+0.5*F10+D10</f>
-        <v>-0.82400000000000162</v>
+        <f>+G10+0.5*F10-D10</f>
+        <v>-37.823999999999998</v>
       </c>
       <c r="I10">
         <f t="shared" si="1"/>
